--- a/data/H1_mechanism_data_2026-08.xlsx
+++ b/data/H1_mechanism_data_2026-08.xlsx
@@ -8,11 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0_README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_Series" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_Plants" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_Permits" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_USGS_alumina" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_USGS_gallium" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_H1_Series" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_H1_Plants" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_H1_Permits" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_H1_USGS_Alumina" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_H1_USGS_Gallium" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,7 +491,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>1_Series</t>
+          <t>11_H1_Series</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -508,7 +508,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2_Plants</t>
+          <t>10_H1_Plants</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -525,7 +525,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>3_Permits</t>
+          <t>13_H1_Permits</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -542,7 +542,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>4_USGS_alumina</t>
+          <t>14_H1_USGS_Alumina</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -559,7 +559,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>5_USGS_gallium</t>
+          <t>15_H1_USGS_Gallium</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -728,873 +728,605 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>H1 Figure 1 series: alumina / Ga capacity &amp; output / Ga price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>cn_gallium_capacity_t</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>cn_gallium_production_t</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>ga_price_lowgrade_usd_kg</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>ga_price_mixed_basis_usd_kg</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>cn_alumina_production_mt</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>sources_note</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>640</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>DUT2002(cap,approx design);MYB2002(price=producer price 99.9999%);MYB2004(alumina)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>4.65</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>640</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>DUT2002(cap,approx design);MYB2002(price=producer price 99.9999%);MYB2004(alumina)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5.45</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2002</v>
+      </c>
+      <c r="D5" t="n">
+        <v>229</v>
+      </c>
+      <c r="E5" t="n">
+        <v>530</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>MYB2003(low-grade import avg,'about same as 2002'→229);MYB2002(mixed=avg US import value);MYB2004(alumina)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6.11</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D6" t="n">
+        <v>225</v>
+      </c>
+      <c r="E6" t="n">
+        <v>411</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>MYB2003(cap tbl7;low-grade 225;mixed);MYB2004(alumina)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6.99</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B7" t="n">
+        <v>47</v>
+      </c>
+      <c r="D7" t="n">
+        <v>192</v>
+      </c>
+      <c r="E7" t="n">
+        <v>550</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>MYB2004(cap tbl7;low-grade);MYB2005(mixed,rev);MYB2007(alumina,rev)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>538</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8.61</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B8" t="n">
+        <v>59</v>
+      </c>
+      <c r="C8" t="n">
+        <v>18</v>
+      </c>
+      <c r="D8" t="n">
+        <v>244</v>
+      </c>
+      <c r="E8" t="n">
+        <v>538</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>MYB2005(cap tbl7;low-grade;mixed);Li2022(prod,Antaike/CNIA);MYB2007(alumina)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13.7</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B9" t="n">
+        <v>59</v>
+      </c>
+      <c r="D9" t="n">
+        <v>285</v>
+      </c>
+      <c r="E9" t="n">
+        <v>443</v>
+      </c>
+      <c r="F9" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>MYB2006(cap tbl7;low-grade;mixed);MYB2007(alumina)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B10" t="n">
+        <v>59</v>
+      </c>
+      <c r="D10" t="n">
+        <v>314</v>
+      </c>
+      <c r="E10" t="n">
+        <v>530</v>
+      </c>
+      <c r="F10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>MYB2007(cap tbl7;low-grade;mixed);MYB2007(alumina)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22.8</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B11" t="n">
+        <v>59</v>
+      </c>
+      <c r="D11" t="n">
+        <v>361</v>
+      </c>
+      <c r="E11" t="n">
+        <v>579</v>
+      </c>
+      <c r="F11" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>MYB2008(cap tbl7;low-grade 361=+15% vs 2007;mixed);MYB2012(alumina)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>449</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>23.8</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B12" t="n">
+        <v>59</v>
+      </c>
+      <c r="D12" t="n">
+        <v>304</v>
+      </c>
+      <c r="E12" t="n">
+        <v>449</v>
+      </c>
+      <c r="F12" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>MYB2009(cap tbl7;low-grade;mixed);MYB2012(alumina)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B13" t="n">
+        <v>141</v>
+      </c>
+      <c r="D13" t="n">
+        <v>307</v>
+      </c>
+      <c r="E13" t="n">
+        <v>600</v>
+      </c>
+      <c r="F13" t="n">
+        <v>29</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>MYB2010(cap tbl7;low-grade 307 'about same as 2009';mixed);MYB2012(alumina)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>34.1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B14" t="n">
+        <v>280</v>
+      </c>
+      <c r="C14" t="n">
+        <v>200</v>
+      </c>
+      <c r="D14" t="n">
+        <v>374</v>
+      </c>
+      <c r="E14" t="n">
+        <v>688</v>
+      </c>
+      <c r="F14" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>MYB2011(cap tbl7;prod reported;low-grade 374=+22% vs 2010;mixed);MYB2012(alumina)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>37.7</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B15" t="n">
+        <v>350</v>
+      </c>
+      <c r="C15" t="n">
+        <v>300</v>
+      </c>
+      <c r="D15" t="n">
+        <v>349</v>
+      </c>
+      <c r="E15" t="n">
+        <v>529</v>
+      </c>
+      <c r="F15" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>MYB2012(cap tbl7;prod reported;low-grade 349;mixed=high-grade 529);MYB2012(alumina)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>44.4</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B16" t="n">
+        <v>450</v>
+      </c>
+      <c r="C16" t="n">
+        <v>300</v>
+      </c>
+      <c r="D16" t="n">
+        <v>276</v>
+      </c>
+      <c r="E16" t="n">
+        <v>502</v>
+      </c>
+      <c r="F16" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>MYB2013(cap tbl7;prod reported;low-grade 276;high-grade 502);MYB2015(alumina)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>47.1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B17" t="n">
+        <v>551</v>
+      </c>
+      <c r="C17" t="n">
+        <v>450</v>
+      </c>
+      <c r="D17" t="n">
+        <v>239</v>
+      </c>
+      <c r="E17" t="n">
+        <v>363</v>
+      </c>
+      <c r="F17" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>MYB2014(cap tbl7;low-grade 239;mixed);MYB2018(prod tbl6,rev);MYB2015(alumina,rev)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>58.98</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B18" t="n">
+        <v>600</v>
+      </c>
+      <c r="C18" t="n">
+        <v>444</v>
+      </c>
+      <c r="D18" t="n">
+        <v>188</v>
+      </c>
+      <c r="E18" t="n">
+        <v>317</v>
+      </c>
+      <c r="F18" t="n">
+        <v>58.98</v>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>MYB2015(cap tbl7;low-grade 188;high-grade 317);MYB2018(prod tbl6);MYB2019(alumina)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>61.03</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B19" t="n">
+        <v>600</v>
+      </c>
+      <c r="C19" t="n">
+        <v>171</v>
+      </c>
+      <c r="D19" t="n">
+        <v>125</v>
+      </c>
+      <c r="E19" t="n">
+        <v>125</v>
+      </c>
+      <c r="F19" t="n">
+        <v>61.03</v>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>MCS2017(cap approx);MYB2020(prod tbl6,rev);MYB2019 tbl1(low-grade);MYB2019(alumina,rev)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>69.02</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B20" t="n">
+        <v>600</v>
+      </c>
+      <c r="C20" t="n">
+        <v>319</v>
+      </c>
+      <c r="D20" t="n">
+        <v>124</v>
+      </c>
+      <c r="E20" t="n">
+        <v>124</v>
+      </c>
+      <c r="F20" t="n">
+        <v>69.02</v>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>MCS2018(cap approx);MYB2020(prod tbl6,rev);MYB2019 tbl1(low-grade);MYB2019(alumina)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>72.53</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B21" t="n">
+        <v>600</v>
+      </c>
+      <c r="C21" t="n">
+        <v>404</v>
+      </c>
+      <c r="D21" t="n">
+        <v>185</v>
+      </c>
+      <c r="E21" t="n">
+        <v>185</v>
+      </c>
+      <c r="F21" t="n">
+        <v>72.53</v>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>MYB2018(cap tbl7);MYB2020(prod tbl6,rev);MYB2019 tbl1(low-grade);MYB2022(alumina)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>72.47</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B22" t="n">
+        <v>600</v>
+      </c>
+      <c r="C22" t="n">
+        <v>338</v>
+      </c>
+      <c r="D22" t="n">
+        <v>153</v>
+      </c>
+      <c r="E22" t="n">
+        <v>153</v>
+      </c>
+      <c r="F22" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>MYB2019(cap tbl7);MYB2020/2022(prod);MYB2020(low-grade,rev);MYB2022(alumina)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>73.79</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B23" t="n">
+        <v>650</v>
+      </c>
+      <c r="C23" t="n">
+        <v>336</v>
+      </c>
+      <c r="D23" t="n">
+        <v>163</v>
+      </c>
+      <c r="E23" t="n">
+        <v>163</v>
+      </c>
+      <c r="F23" t="n">
+        <v>73.79000000000001</v>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>MYB2020(cap tbl7);MYB2022(prod tbl7,rev);MYB2022(low-grade);MYB2022(alumina,rev)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>423</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>77.48</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B24" t="n">
+        <v>650</v>
+      </c>
+      <c r="C24" t="n">
+        <v>423</v>
+      </c>
+      <c r="D24" t="n">
+        <v>254</v>
+      </c>
+      <c r="E24" t="n">
+        <v>254</v>
+      </c>
+      <c r="F24" t="n">
+        <v>77.48</v>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>MYB2021(cap tbl7);MYB2022(prod tbl7);MYB2022(low-grade);MYB2022(alumina,rev)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>81.86</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C25" t="n">
+        <v>600</v>
+      </c>
+      <c r="D25" t="n">
+        <v>394</v>
+      </c>
+      <c r="E25" t="n">
+        <v>394</v>
+      </c>
+      <c r="F25" t="n">
+        <v>81.86</v>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>MYB2022(cap tbl6);MYB2022/MCS2024(prod);MYB2022(low-grade);MYB2022(alumina)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C26" t="n">
+        <v>600</v>
+      </c>
+      <c r="D26" t="n">
+        <v>290</v>
+      </c>
+      <c r="E26" t="n">
+        <v>290</v>
+      </c>
+      <c r="F26" t="n">
+        <v>82</v>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>MCS2024(cap est);MCS2024(prod est);MCS2024(low-purity price);MCS2024(alumina est)</t>
         </is>
@@ -1611,7 +1343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1631,2916 +1363,2842 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>H1 Figure 2 base table: 44 alumina refineries (Chinese source text kept verbatim).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>plant_name</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>province</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>group_owner</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>alumina_capacity_kt</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>host_commissioning_year</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>commissioning_source</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>ore_source</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>process_route</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>gallium_status</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>gallium_operator</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>gallium_capacity_t</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>gallium_line_year</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>gallium_line_year_confidence</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>evidence_summary</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>中铝山东有限公司（原山东铝厂/五〇一厂）</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>山东</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>中国铝业集团</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2560</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>1954</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>中国有色网2025建厂纪实：1954年2月焙烧出第一批氧化铝，7月1日正式投产</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>进口矿</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>拜耳法（历史曾用烧结法/联合法）</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>自营</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>1956</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>中铝山东官网：1957年七月五〇一厂生产镓1853公斤；中国有色网2025：1956年在氧化铝生产中提炼出金属镓。中国最早的提镓电路</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>中铝河南分公司/中铝矿业（郑州上街）</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>河南</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>中国铝业集团</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>1900</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1966</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>中国有色金属报2008建厂50年文：1958-08-20一期开工，1966年投产17.7万吨</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>国产矿</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>混联法→选矿拜耳法</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>自营</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>pre-2008</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>同文列主要产品含金属镓20吨；Chalco英文产品页列河南分公司为四大产镓分公司之一</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>中铝山西新材料（运城河津）</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>山西</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>中国铝业集团</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>2600</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>1987</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>中国有色金属报2023建厂50周年文：1987年一期20万吨氧化铝工程建成</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>国产矿为主</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>一期烧结法/二期混联法/三期石灰拜耳法</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>自营</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Chalco英文产品页列山西分公司为四大产镓分公司之一；USGS OFR2026-1018河津坐标列25t</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>中铝中州铝业（焦作修武）</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>河南</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>中国铝业集团</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>2700</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>1993</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>中铝分子公司简介：1987年开工，1993年建成投产，一期20万吨，烧结法</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>烧结法→碱石灰强化烧结法</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>absent</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>★关键阴性：Chalco英文产品页枚举四家产镓分公司（河南/广西/遵义/山西）不含中州；本项目排污许可指纹阴性。属'权威盘点未列入'型证据，强度中等</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>河南有色汇源铝业（鲁山梁洼）</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>河南</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>神火股份控股（原河南有色金属集团）</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>2004</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>新浪财经2006-02-12：30万吨氧化铝项目2004年7月投产；始建1993年10月为全国第一家民营氧化铝企业（早期规模不详）；产能45→80万吨（神火股份公告2020-030）</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>国产矿（平顶山/鲁山本地矿）</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>拜耳法（推断：方源模式需拜耳循环母液）</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>第三方：珠海方源（六基地之一）</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>2005-2011</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>方源董事长2019受访自列'河南鲁山'为六基地之一（对应USGS Lushan County Refinery，坐标吻合梁洼镇）；方源2019自述仅山西基地在运行→鲁山镓线已停；宿主2019-07起全线停产、2020-06-24鲁山法院受理破产重整。★设施级退出实例：镓线停、宿主破产——但全国产能总量（图一）未降</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>中铝广西分公司（平果铝）</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>广西</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>中国铝业集团</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>2210</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>1995</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>中铝官网2024-07-22：1995年9月25日全国第一家年产30万吨全砂状氧化铝企业建成投产</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>国产矿（自有平果铝土矿）</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>拜耳法</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>自营</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>pre-2014</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>91金属网2026-02：中铝广西已建成年产120吨金属镓生产系统；中铝2014产品页列平果为四大镓厂之一</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>南川先锋氧化铝</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>重庆</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>博赛矿业集团</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>中国有色网2007-03-27：一期2003年9月投产（7万吨/年），二期2005年6月投产</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>国产矿（南川铝土矿）</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>拜耳法</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>第三方：珠海方源</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>2005-2011</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>USGS镓层Nanchuan Refinery运营方为Zhuhai SEZ Fangyuan；方源六厂建于2005-2011（董事长2019受访）。★该厂已于2022-03-27整体关停</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>茌平信发华宇氧化铝</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>山东</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>信发集团</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>8000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>2005</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>生态环境部2008清洁生产标准编制说明：2006年产量174万吨、2006年底产能320万吨→首条线≤2005；澎湃：信发华宇成立于2005年1月</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>进口矿</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>拜耳法</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>本项目排污许可指纹阴性；方源2016年称合作方含山东信发集团但未指明茌平厂。集团内分化：信发山西点位有镓，山东本部无直接证据</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>开曼铝业（三门峡）</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>河南</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>杭州锦江集团</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>2200</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>2005</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>新京报2022-12-15：2003年成立，第一条氧化铝生产线2005年12月投产，初期40万吨</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>自营</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>290</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>券商研报：2022年镓产能160t→2023年产能290t、产量203t≈全球35%（本项目档案）。全球最大镓生产商，但主体排污许可指纹阴性（镓线疑独立核算）</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>洛阳香江万基铝业（新安）</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>河南</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>香江集团+万基控股</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>1400</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>2005</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>2019中国有色网大盘点列2005年（二手）；中国有色金属报2015-02-11：140万吨项目全面投产</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>国产矿</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>拜耳法</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>自营</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>★关键：我的钢铁2025-06-12环评'全厂新增副产品金属镓60吨/年，氧化铝产能保持不变'——'新增'二字证明2025年前该厂无镓线。宿主2005年建成，20年后才装</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>山东魏桥铝电（邹平）</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>山东</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>中国宏桥/魏桥创业集团</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>中国有色网2006-07-17：一条年产能50万吨的新建氧化铝生产线7月正式投入商业生产，为一期</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>进口矿（几内亚、澳大利亚）</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>拜耳法</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>site_positive_entity_negative</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>第三方：珠海方源（历史）</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>2005-2011</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>⚠法人分离：宏桥控股2026-06-04'公司现阶段未开展与金属镓相关的生产活动'；但方源董事长2019自列'山东邹平'为六基地之一，邹平县唯一氧化铝厂即魏桥。当前运行状态不明</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>东方希望（三门峡）铝业（渑池）</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>河南</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>东方希望集团</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>2800</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>新浪财经2026-03-10：2003年成立，2006年生产线投产</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>拜耳法</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>自营（蓝晓科技承建）</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>蓝晓科技2021问询函回复：2008年为东方希望（三门峡）建成年产70吨4N高纯镓线，为国内当年单厂产能最大的氧化铝母液提镓线</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>国家电投集团山西铝业（忻州原平）</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>山西</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>国家电投集团</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>2800</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>中国有色金属报2014-12-12：中电投山西铝业于2006年投产，年产规模260万吨</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>国产矿（晋北煤铝）</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>串联法（我国第一条）</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>第三方：原平中科晶电镓业；USGS另列珠海方源</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>2021-06</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>中科晶电集团生产基地页：原平中科晶电镓业，金属镓年产100吨，2021年6月投产；USGS将Yuanping Refinery镓线运营方记为方源（更早的一层）</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>龙口东海氧化铝</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>山东</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>南山集团/南山铝业</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>1800</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>生态环境部2008编制说明：南山2006年产量5万吨、年底产能50万吨；企业简介：2003年8月经国家批准建设</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>进口矿（印尼、印度、澳洲）</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>拜耳法（澳式两段分解）</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>absent</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>★关键阴性：每日经济新闻2023-07-19南山铝业投资者互动'公司持续关注从赤泥中提取金属镓的可行性'——2023年仍停留在'关注'阶段</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>广西华银铝业（百色德保）</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>广西</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>广西投资集团（中铝参股）</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>2200</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>中铝转载广西日报：2007年12月28日第一条生产线投产；2008年6月18日4条线全面投产</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>国产矿（靖西、德保自有矿）</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>拜耳法</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>第三方：广西德保镓业（与广东先导合作）</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>pre-2021</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>91金属网2026-02：华银铝与广东先导从氧化铝母液提取氢氧化镓，年产能折合金属镓约100吨；蓝晓2021问询函客户名单含德保镓业；我的钢铁2024-10德保镓业拟由640吨扩至2000吨粗氢氧化镓</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>山东鲁北海生生物</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>山东</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>山东鲁北企业集团</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>公司官网：公司于2007年3月建成投产</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>进口矿（三水铝土矿）</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>拜耳法（低温管道化溶出）</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>未检索到任何镓相关信息</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>广西信发铝电（百色靖西）</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>广西</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>信发集团</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>中国有色网2015-05-07：2008年4月25日年产240万吨氧化铝项目第一条生产线竣工投产</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>国产矿（自有靖西/龙州铝土矿）</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>拜耳法</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>疑第三方珠海方源；另有信发自建高纯镓示范项目</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>pre-2015</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>中国有色网2015-05-07：延伸产业链条，开创广西提镓项目之先河；USGS镓层Jingxi Refinery运营方为方源。★USGS氧化铝层完全遗漏此厂（全国第7大）</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>山西兆丰铝电（阳泉）</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>山西</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>华阳新材料+信发</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>1100</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>2019中国有色网大盘点列2008年（二手汇编）</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>头豹报告列'山西昭丰60t/a'，与'兆丰'是否同一主体未确认</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>遵义铝业股份（原中铝遵义氧化铝）</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>贵州</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>中国铝业集团</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>中国有色网2012-03-16：2010年底项目建成试产（80万吨）</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>国产矿（高硫一水硬铝石，选矿脱硫）</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>拜耳法配选矿脱硫</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>自营（蓝晓科技建线）</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>中国有色网2012-05-11：年产40吨镓金属项目为当时全国一次性投入规模最大的镓生产线，树脂吸附法；新华网2024-05-17：遵义铝业占据国内10%的镓产能。⚠本项目档案记'2014中止'未获证实，与2024年报道冲突，待落实</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>中铝重庆分公司（南川80项目）</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>重庆</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>中国铝业集团</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>重庆市发改委：2010年10月28日正式投料试车（2007-03-18开工）</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>国产矿（低品位高硫铝土矿）</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>联合法（选矿脱硫串联法）</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>中国有色网2012-11-06规划'形成年产20吨金属镓'——仅规划，未见建成/投产证据</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>山西信发交口肥美铝业</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>山西</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>信发集团</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>2400</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>2019中国有色网大盘点列2011年（二手汇编）</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>未找到镓相关证据</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>云南文山铝业</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>云南</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>云铝股份（中铝系）</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>1400</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>云铝文山铝业2022-12-22：2012年80万吨氧化铝项目建成投产；2016年二期60万吨</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>国产矿（低品位复杂难处理铝土矿）</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>拜耳法</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>自营</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>★三次表态连成时间线：南都2023-07-11'未生产金属镓产品'→每经2024-10-22'金属镓项目正在推进中，尚未投产'→证券之星2025-06-12'金属镓项目已建成投运'、2026-05-14'已建成投运50吨/年'。宿主2012年建成，13年后才装</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>山西华兴铝业（吕梁兴县）</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>山西</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>中国铝业股份</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>1800</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>中铝官网：一期2013年10月建成投产（80万吨），二期2016年4月建成投产（100万吨）</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>进口矿</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>拜耳法</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>人民网2023-04投产仪式报道（本项目档案）；排污许可2023-12-29重新申请；新浪财经2025-07引普华有策：山西华兴等新增/扩建产能逐渐释放</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>柳林县森泽煤铝</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>山西</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>山西森泽能源科技集团</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>森泽集团简介：2013年起完成60万吨/年氧化铝项目建设（起始年份存歧义）</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>国产矿（自有铝土矿）</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>拜耳法</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>第三方：森泽系镓业公司</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>柳林新闻网2021-12-22：金属镓项目于2019年开始建设，2020年投产运行，产能40T/年</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>山西复晟铝业（运城平陆）</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>山西</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>杭州锦江集团+郑煤集团</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>中国有色金属报2016-12-28：一期年产80万吨，2014年10月投产</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>国产矿（平陆当地铝土矿）</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>第三方：平陆优英镓业</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>pre-2021</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>蓝晓科技2021问询函列平陆优英为国内具备镓产能企业之一；头豹报告列平陆优英40t/a</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>贵州华锦铝业（贵阳清镇）</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>贵州</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>中国铝业控股+杭州锦江参股</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>1600</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>中国有色网2015-05-04：一期年产80万吨2015年4月29日投产；国资委2018-11-14同述</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>国产矿（黔中一水硬铝石）</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>拜耳法</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>自营</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>2024-11</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>★中铝官网2024-11-20《贵州华锦金属镓项目建成投产》；中冶有色标题《从铝土矿中提取金属镓，年产50吨项目建成投产》。宿主2015年建成，9年后才装（正文被robots拦截，仅得标题与日期）</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>中铝交口兴华科技</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>山西</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>中国铝业股份控股</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>900</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>矿产资源网：一期35万吨2015年5月投产，二期55万吨2017年6月投产</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>公司页称计划发展'金属镓—砷化镓产业链'，仅规划，无投产证据</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>广西田东锦鑫化工</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>广西</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>杭州锦江集团</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>2200</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>我的钢铁2023-05-12：120万吨线2023年投产；此前100万吨技改2018年8月竣工环保验收</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>混合</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>拜耳法</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>未检索到任何提镓环评、招投标或新闻</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>靖西天桂铝业</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>广西</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>天山铝业</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>2500</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>百色市政府：天桂铝业一期80万吨氧化铝于2019年年底实现竣工投产；2022上半年全面投产</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>混合（广西自有矿+印尼/几内亚进口矿）</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>拜耳法</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>absent</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>★关键阴性：提镓专利CN116081688A已于2024-04-30驳回；天山铝业2024/2025年报摘要无'镓'字；SMM2023记其仍在'论证'赤泥提镓；排污许可指纹阴性；无环评/招投标/投产报道</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>广西华昇新材料（防城港）</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>广西</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>中国铝业51%+广西投资集团39%</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>4000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>澎湃2021-01-29：2020年7月22日Ⅰ系列成功投料试车，10月28日200万吨全线投产</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>进口矿（几内亚）</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>拜耳法</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>unknown（倾向absent）</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>★否证'新建厂出厂即带镓电路'：排污许可（2019-12-16首次核发）指纹阴性；中铝二期报道亦无镓字；未见任何提镓环评/招投标/新闻</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>重庆九龙万博新材料（万州）</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>重庆</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>博赛矿业集团</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>3600</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>重庆市政府2025-05-06：项目2020年9月开工，用时18个月建成投产，设计年产能360万吨</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>进口矿（几内亚、澳大利亚三水铝石）</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>拜耳法（低温溶出）</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>第三方：重庆先导再生资源（广东先导系）</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>重庆市生态环境局环评公示2024-07-24：重庆先导再生资源年产150吨金属镓产业化项目，厂址万州经开区九龙园，与九龙万博同址；重庆市政府2023-03-24：九龙万博计划与其他机构合作提取金属镓、钒。⚠环评'原料依托'一节未读到，机制链条最后一环缺原文</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>国家电投贵州遵义产业发展（务川）</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>贵州</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>国家电投集团</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>91金属网2024-03-20：一期年产100万吨氧化铝厂已建成投产（发改委2014核准务正道80万吨项目）</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>国产矿（务正道铝土矿）</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>拜耳法</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>未检索到提镓环评/新闻；USGS氧化铝层未收录该厂</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>汇宏新材料（滨州沾化临港）</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>山东</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>中国宏桥/魏桥创业集团</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>8000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>pre-2019</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>未找到首条线年份；2019年行业盘点已列400万吨（二期）；400万吨迁建升级项目2024-10投产200万吨、2025-05全部投产</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>进口矿</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>拜耳法</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>第三方：滨州镓元新材料</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>2025-2026</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>滨州市2025年市重点项目名单第54项：滨州镓元新材料有限公司氧化铝循环母液提取金属镓项目；行业媒体称方源持股24%、一期30t、远期120t，原料来自汇宏——该三项仅一个二手来源，待二次确认</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>孝义市兴安化工</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>山西</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>杭州锦江集团</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>2800</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>未找到</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>第三方：孝义兴安镓业（本项目排污许可查得，首次核发2020-03-31）</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>头豹研究院2023镓行业概览产能表列'孝义兴安 120t/a'，为国内最大民营产镓商；本项目排污许可：孝义市兴安镓业有限公司位于兴安化工厂内，执行稀土工业排放标准GB26451，工商年报≤2013</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>山西信发化工（孝义）</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>山西</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>信发集团</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>3600</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>未找到</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>未找到镓相关证据</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>东方希望晋中铝业（左权）</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>山西</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>东方希望集团</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>仅查到二期三线2018-09-28投产，一期年份未找到</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>未找到镓相关证据</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>山西同德铝业</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>山西</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>同煤+阳煤+信发</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>2019大盘点仅记2011年获批，投产年份未找到</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>国内矿</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>未找到镓相关证据</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>河南中美铝业（登封告成）</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>河南</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>永煤集团70%+五洲铝业20%+登电集团10%</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>中国有色网2011-06-30：一期40万吨于2007年10月20日全面投产，总设计80万吨</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>国产矿（登封陈楼等本地铝土矿）</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>拜耳法</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>第三方：珠海方源（六基地之一）</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>2008-2011</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>方源董事长2019受访自列'河南登封'为六基地之一（对应USGS Dengfeng Refinery，告成镇）；方源2019自述仅山西基地在运行→登封镓线已停；宿主2023年起70%股权反复挂牌（2026年2/5/6月三次）。⚠USGS另一条Dengfeng Aluminium Factory(Suspended)实为登电集团约4万吨电解铝/合金厂，非氧化铝厂，疑归类错误</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>山西其亚铝业</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>山西</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>其亚集团</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>2400</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>cnmn2019列为在建240万吨，后投产（投产年份未单独核实，约2021-2023）</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>抽样框补充行，未检索镓证据</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>贵州其亚铝业（福泉）</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>贵州</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>其亚集团</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>cnmn2019列100万吨</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>自营</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>20（一期；三期规划60）</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>贵州其亚铝业氢氧化铝厂区提镓线：首期20吨2023-10-08建成投产，二期2024-09投产，三期规划共60吨（网易/搜狐转载企业报道，2024）。第二波实例，且在A场公告之后——属反身性侵蚀证据</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>贵州广铝氧化铝（清镇）</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>贵州</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>广铝集团</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>cnmn2019列80万吨</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>present</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>新浪财经2025-07引普华有策：'山西华兴、平陆优英、中科晶电、中铝广西二期、贵州广铝等主要生产厂商新增、扩建产能逐渐释放'→有镓产能（第二波），投产年份与规模未核</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>河北文丰新材料（唐山曹妃甸）</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>河北</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>文丰集团</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>4800</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>新华社2025-05-08：2023年3月全部投产；以氢氧化铝名义立项，合规争议被点名</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>进口矿</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>拜耳法（推断）</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>抽样框补充行（七省市之外最大新增），未检索镓证据</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>河北文丰钢铝产业</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>河北</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>文丰集团</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>4800</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>方正中期/钢联2025：2025年5月投产</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>进口矿</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>抽样框补充行，未检索镓证据</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>内蒙古致轩新材料（达拉特旗）</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>内蒙古</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>致轩（民营）</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>新浪期货2024-05：一期100万吨计划2024年分两批投产（达产状态未完全证实）</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>抽样框补充行，未检索镓证据</t>
         </is>
@@ -4557,7 +4215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4575,990 +4233,969 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>permit_no</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>first_issue_date</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>industry_class</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>host_or_site</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>hcl_flag</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>h2so4_mist_flag</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>fingerprint</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>gallium_status</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>corroborating_evidence</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="L1" s="4" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>三门峡台泉镓业科技有限公司</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>91411200MAE9CKQ814001V</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>隔热和隔音材料制造</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>河南三门峡示范区</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>positive_weak</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>dedicated_gallium_firm</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>平台登记;2026 新设</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>管制后新生儿——反身性侵蚀证据(管制→涨价→新产能);不入 H1 主面板</t>
         </is>
       </c>
-      <c r="L2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>朝阳金美镓业有限公司</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>91211300MA0XYDACX4001Q</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2019-12-19</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>电子专用材料制造</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>辽宁朝阳喀左(无铝厂)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>positive_strong</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>dedicated_gallium_firm</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>废水含总砷→疑砷化镓回收/提纯路线</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>六家专业户中首证最早;归回收/提纯层,非拜耳法一次镓</t>
         </is>
       </c>
-      <c r="L3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>孝义市兴安镓业有限公司</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>9114118157106426XT001U</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>2020-03-31</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>其他稀有金属冶炼</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>山西孝义兴安化工厂内(信发系)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>positive_strong</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>dedicated_gallium_firm</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>工商年报≤2013;执行稀土工业排放标准GB26451</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>许可日≠始建日(制度2017后铺开);信发系山西点位</t>
         </is>
       </c>
-      <c r="L4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>原平中科晶电镓业有限公司</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>91140981MA0MRHLP9E001V</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>2022-05-26</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>其他稀有金属冶炼</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>国家电投集团山西铝业厂区内</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>positive_weak</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>dedicated_gallium_firm</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>专利 CN118957314B(2024-07)</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>新发现宿主:国家电投山西铝业;定年由专利2024提前至2022</t>
         </is>
       </c>
-      <c r="L5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>平陆优英镓业有限公司</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>91140829MA0K9U196K001V</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>2020-06-24</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>其他稀有金属冶炼</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>山西运城平陆</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>positive_strong</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>dedicated_gallium_firm</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>蓝晓2021问询函客户名单</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>客户名单+许可双重印证</t>
         </is>
       </c>
-      <c r="L6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>广西德保镓业有限公司</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>91451024581985767L001Z</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>2024-03-28</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>其他稀有金属冶炼</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>德保华银铝厂区</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>positive_weak</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>dedicated_gallium_firm</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>蓝晓2021客户;2024 环评扩建报道</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>宿主坐实:华银铝;许可晚于实际运营</t>
         </is>
       </c>
-      <c r="L7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>柳林县森泽方源镓业科技有限公司</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>91141125075547211Y001V</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>2020-12-08</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>其他稀有金属冶炼</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>柳林森泽公司厂区</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>positive_weak</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>dedicated_gallium_firm</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>平台新发现</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>全新面孔+新宿主(森泽,柳林煤铝系)</t>
         </is>
       </c>
-      <c r="L8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>开曼铝业（三门峡）有限公司</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>914112007507048163001P</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>2018-06-02</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>铝冶炼+煤制合成气</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>自有氧化铝(三门峡)</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>negative</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>known_gallium_major</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>副本载投产日期2005-12-26;券商:2022产能160t→2023产能290t/产量203t=全球35%</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>全球最大镓厂但主体许可指纹阴性(镓线可能独立核算或排放并入他证);2022-04重新申请疑为扩产时点</t>
         </is>
       </c>
-      <c r="L9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>东方希望（三门峡）铝业有限公司</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>91411200753877093M001P</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>2017-05-27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>铝冶炼</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>自有氧化铝(渑池天坛工业园)</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>positive_strong</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>gallium_line_inferred_from_fingerprint</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>蓝晓2008建70t/y 4N高纯镓线;新华财经2022:三门峡高纯镓产能110t占全国27.1%</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>★指纹法首个战果:许可证只写铝冶炼,排放清单(HCl+硫酸雾+酚类)出卖提镓线</t>
         </is>
       </c>
-      <c r="L10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>山西华兴铝业有限公司</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>9114000055870084XW001P</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>2017-06-14</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>铝冶炼</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>自有氧化铝(吕梁兴县)</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>positive_weak</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>gallium_line_confirmed</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>人民网2023-04投产仪式;许可2023-12-29重新申请</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>投产仪式与许可变更时间线咬合(4月→12月)</t>
         </is>
       </c>
-      <c r="L11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>靖西天桂铝业有限公司</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>91451025MA5KYFWF7J001P</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>2019-07-19</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>铝冶炼</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>自有氧化铝(广西靖西)</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>negative</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>patent_only_no_line</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>专利 CN116081688A(2022-12-30)已于2024-04-30驳回;天山铝业2025年报无"镓"字;SMM2023记其仍在"论证"赤泥提镓</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>★关键阴性(2026-08复核加强):专利被驳回、无环评/招投标/投产报道、年报无镓→确证未装线。注意靖西另有广西信发铝电(300万吨,2008投产),USGS氧化铝层遗漏该厂;USGS标在靖西的方源镓点宿主应为信发而非天桂(方源6厂建于2005-2011,天桂2019底才投产)</t>
         </is>
       </c>
-      <c r="L12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>广西华昇新材料有限公司</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>91450600MA5L65WW7U001P</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>2019-12-16</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>铝冶炼</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>中铝广西防城港基地</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>negative</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>no_gallium_evidence</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>★否证'新建厂出厂即带镓电路';政策指令变量需按具体文件细化</t>
         </is>
       </c>
-      <c r="L13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>中铝中州铝业有限公司</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>914108213357726196001P</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>2017-05-28</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>铝冶炼</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>中铝河南修武</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>negative</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>no_gallium_evidence</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>中铝2014产品页四大镓厂不含中州</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>大厂而无镓:H1 因变量变异的来源</t>
         </is>
       </c>
-      <c r="L14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>遵义铝业股份有限公司氧化铝区</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>91520321785494580T001P(现006V)</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>2017-06-29</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>铝冶炼</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>中铝贵州遵义</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>negative</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>known_gallium_but_negative</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>中铝2014产品页列为四大镓厂;2002论文:2001年中试产镓;蓝晓2012建40t/y线2014中止</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>★指纹法边界样本:已知有镓却阴性→碳分法不产酸性废气/线已停/规模过小;确立'阳性=强证据,阴性≠无镓'</t>
         </is>
       </c>
-      <c r="L15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>茌平信发华宇氧化铝有限公司</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>91371500769712461N001P</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>2017-06-23</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>铝冶炼</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>信发系山东本部</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>negative</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>no_gallium_evidence</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>集团内分化:信发山西(兴安镓业)有镓,山东本部无→厂级而非集团级决策</t>
         </is>
       </c>
-      <c r="L16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>山东魏桥铝电年产400万吨氧化铝生产线</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>9137160074568737XQ024P</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>2018-12-26</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>铝冶炼</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>宏桥/魏桥邹平</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>negative</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>legal_entity_negative_site_positive</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>宏桥控股(002379)2026-06-04互动易"公司现阶段未开展与金属镓相关的生产活动";方源董事长2019受访自列"山东邹平"为其6个镓基地之一;2025-26滨州镓元新材料(方源持股24%)30t线落地沾化</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>原料来自魏桥系汇宏新材料</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>宏桥控股(002379)2026-06-04互动易"公司现阶段未开展与金属镓相关的生产活动";方源董事长2019受访自列"山东邹平"为其6个镓基地之一;2025-26滨州镓元新材料(方源持股24%)30t线落地沾化,原料来自魏桥系汇宏新材料</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>⚠对照组已作废(2026-08复核):铝厂法人口径无镓属实,但厂区/母液层面有第三方镓电路→'能装而未装'的说法必须撤回;正确读法=外包电路(法人分离,母液供给),这是H1的机制发现而非反例</t>
         </is>
@@ -5591,1348 +5228,1347 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>facility_name</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>operator</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>ultimate_owner</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>owner_pct</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>province</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>county_or_city</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitude</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitude</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>capacity_kt</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Nanchuan Refinery</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Nanchuan Pioneer Alumina Refinery Co., Ltd.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Bosai Minerals Group Co., Ltd.</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Chongqing</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Chongqing, Nanchuan District, Wenfeng</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>29.1089</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>107.05</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Plant in Chongqing</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Aluminum Corp. of China (Chinalco)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Government</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Chongqing</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Chongqing</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>30.1</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>107.72</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Guangxi Huayin Refinery</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Guangxi Huayin Aluminium Industry Co., Ltd.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Guangxi Investment Group Co.</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>33.4%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Guangxi</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Guangxi, Baise, Debao County</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>23.3836</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>106.587</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>2200</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Pingguo Refinery</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Aluminum Corp. of China (Chinalco)</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Government</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Guangxi</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Guangxi, Baise, Pingguo</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>23.3356</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>107.503</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>2210</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Plant in Baise</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Guangxi Tiandong Jinsheng Chemical Co., Ltd.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Hangzhou Jinjiang Group</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Guangxi</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Guangxi, Baise, Tiandong County</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>23.6488</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>107.126</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Plant in Gangkou District</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Aluminum Corp. of China (Chinalco)</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Government</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Guangxi</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Guangxi, Fangchenggang, Gangkou District</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>21.5588</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>108.443</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Plant in Jingxi</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Jingxi Tiangui Aluminum Co., Ltd.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Tianshan Aluminum Co., Ltd.</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Guangxi</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Guangxi, Baise, Jingxi</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>23.15</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>106.43</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Guizhou Huajin Plant</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Aluminum Corp. of China (Chinalco)</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Government</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Guizhou</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Guizhou, Guiyang, Qingzhen</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>26.7938</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>106.273</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>1600</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Plant in Bonan</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Aluminum Corp. of China (Chinalco)</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Government</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Guizhou</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Guizhou, Zunyi, Bozhou District, Bonan</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>27.5235</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>106.842</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Henan Smelter</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Aluminum Corp. of China (Chinalco)</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Government</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Henan</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Henan, Zhengzhou, Shangjie District</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>34.8169</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>113.273</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>2410</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Plant in Mianchi County</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Oriental Hope Aluminum Co., Ltd.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>East Hope Group Co., Ltd.</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Henan</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Henan, Sanmenxia, Mianchi County</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>34.804</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>111.798</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>2200</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Plant in Shangjie District</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Aluminum Corp. of China (Chinalco)</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Government</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Henan</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Henan, Zhengzhou, Shangjie District</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>34.81</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>113.3</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Plant in Xin'An County</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Luoyang Xiangjiang Wanji Aluminum Industry Co., Ltd.</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Wanji holiding Group Co., Ltd.</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Henan</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Henan, Luoyang, Xin'An County</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>34.7363</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>112.049</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>1400</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Zhongzhou Refinery</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Aluminum Corp. of China (Chinalco)</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Government</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Henan</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Henan, Jiaozuo, Xiuwu County</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>35.3768</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>113.446</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>3050</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Plant in Longkou</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Longkou Donghai Alumina Co., Ltd.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Shandong Nanshan Aluminum Co., Ltd.</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Shandong</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Shandong, Yantai, Longkou</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>37.7229</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>120.448</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>1400</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Plant in Wudi County</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>China Hongqiao Group Ltd.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>China Hongqiao Group Ltd.</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Shandong</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Shandong, Binzhou, Wudi County</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>38.073</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>117.729</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Plant in Zhangdian District</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Aluminum Corp. of China (Chinalco)</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Government</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Shandong</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Shandong, Zibo, Zhangdian District</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>36.7552</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>118.049</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>2270</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Shandong Weiqiao Refinery</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Shandong Weiqiao Aluminum and Electricity Co., Ltd.</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>China Hongqiao Group Ltd.</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Shandong</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Shandong, Binzhou, Zouping</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>36.903</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>117.761</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>15000</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Plant in Hejin</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Aluminum Corp. of China (Chinalco)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Government</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Shanxi</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Shanxi, Yuncheng, Hejin</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>35.6566</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>110.668</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>2600</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Plant in Yangquan</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Huayang New Material Technology Group Co., Ltd.</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Huayang New Material Technology Group Co., Ltd.</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr"/>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Shanxi</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Shanxi, Yangquan</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>37.86</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>113.58</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>1100</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Plant in Yuanping</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>SPIC Shanxi Aluminum Co., Ltd.</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>State Power Investment Corp. Ltd. (Government)</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Shanxi</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Shanxi, Xinzhou, Yuanping</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>38.7853</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>112.756</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>2900</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Plant in Zuoquan County</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Oriental Hope Aluminum Co., Ltd.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>East Hope Group Co., Ltd.</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Shanxi</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Shanxi, Jinzhong, Zuoquan County</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>37.04</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>113.46</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>2400</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Shanxi Huaxing Refinery</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Aluminum Corp. of China (Chinalco)</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Government</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Shanxi</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Shanxi, Luliang, Xing County</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>38.47</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>111.14</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Xinghua Technology Plant</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Aluminum Corp. of China (Chinalco)</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Government</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Shanxi</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Shanxi, Luliang, Jiaokou County</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>36.95</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>111.3</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>900</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Plant in Wenshan</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Yunnan Wenshan Aluminum Co., Ltd.</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Yunnan Aluminium Co., Ltd. (Chinalco)</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Yunnan</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Yunnan, Wenshan Zhuang and Miao Autonomous Prefecture</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>23.4558</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>104.13</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>1400</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
@@ -6966,937 +6602,929 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>facility_name</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>operator</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>ultimate_owner</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>province</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>county_or_city</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>latitude</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>longitude</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>capacity_t</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>host_type</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>verification_note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Nanchuan Refinery</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Zhuhai SEZ Fangyuan Inc.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Zhuhai SEZ Fangyuan Inc. (private, Zhuhai)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Chongqing</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Chongqing, Nanchuan</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>29.16</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>107.17</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Unverified</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>alumina</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>CORRECTED 2026-08: capacity was 130 in GIS attr table = Fangyuan COMPANY-WIDE total across 6 plants (Asian Metal interview w/ chairman, 2019); USGS OFR 2026-1018 tbl5 lists NA. USGS ultimate_owner 'Chinalco' is an error — Fangyuan is private. Built 2005-2011.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Danxia Zinc Smelter</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Shenzhen Zhongjin Lingnan Nonfemet Co., Ltd.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Shenzhen Nonfemet Co., Ltd.</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Guangdong</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Guangdong, Shaoguan</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>25.111</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>113.662</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>zinc</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>non-Bayer host: the 5% zinc route (USGS MYB2022 citing Juncong 2017)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Jingxi Refinery</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Zhuhai SEZ Fangyuan Inc.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Zhuhai SEZ Fangyuan Inc. (private, Zhuhai)</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Guangxi</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Guangxi, Jingxi</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>23.16</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>106.34</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Unverified</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>alumina</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>HOST RE-ASSIGNED 2026-08: host is almost certainly Guangxi Xinfa Aluminum &amp; Power (alumina line commissioned 2008-04-25, 3.0 Mt) — NOT Jingxi Tiangui (first alumina line commissioned end-2019, after Fangyuan's 2005-2011 build window). Xinfa is MISSING from the USGS alumina layer. Coordinate offsets cannot discriminate (USGS Ga-to-host offsets run 1.7-13.0 km).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Pingguo Smelter</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Pingguo Aluminum Co., Ltd.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Chinalco (Government)</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Guangxi</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Guangxi, Baise, Pingguo</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>23.336</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>107.496</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>alumina</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Chinalco Guangxi reported at 120 t Ga4N as of 2026 (91jinshu 2026-02) — capacity field likely stale</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Plant in Bonan</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Aluminum Corp. of China (Chinalco)</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Government</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Guizhou</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Guizhou, Zunyi, Bozhou District, Bonan</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>27.5235</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>106.842</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>alumina</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Zunyi Smelter</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Aluminum Corp. of China (Chinalco)</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Chinalco (Government)</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Guizhou</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Guizhou, Zunyi</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>27.515</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>106.837</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>alumina</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>USGS OFR 2026-1018 gives 150 for Zunyi vs 40 in GIS attr table — two vintages, do not mix</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Dengfeng Aluminium Factory</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Dengfeng Power Group Co., Ltd.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Dengfeng Power Group Co., Ltd.</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Henan</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Henan, Zhengzhou, Dengfeng</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>34.38</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>113.13</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Suspended</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>alumina</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Dengfeng Refinery</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Zhuhai SEZ Fangyuan Inc.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Zhuhai SEZ Fangyuan Inc. (private, Zhuhai)</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Henan</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Henan, Dengfeng</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>34.4</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>113.04</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Unverified</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>alumina</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>see Nanchuan note: 130 was company-wide, USGS pub says NA</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Henan Refinery</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Aluminum Corp. of China (Chinalco)</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Henan Branch China Aluminium</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Henan</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Henan, Zhengzhou, Shangjie District</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>34.8168</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>113.273</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>alumina</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Lushan County Refinery</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Zhuhai SEZ Fangyuan Inc.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Zhuhai SEZ Fangyuan Inc. (private, Zhuhai)</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Henan</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Henan, Lushan County</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>33.73</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>112.8</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Unverified</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>alumina</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>see Nanchuan note</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Chengmenshan Mine</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Jiangxi Copper Corp.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Jiangxi Copper Corp.</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Jiangxi</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Jiangxi, Chaisang District, Sai Lake</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>29.6867</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>115.799</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>copper</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>non-Bayer host</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Plant in Yantai</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr"/>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Shandong</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Shandong, Yantai</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>36.68</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>120.5</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Suspended</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>alumina</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Plant in Zibo</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Shandong Aluminium Industry Co., Ltd.</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Shandong Aluminium Industry Co., Ltd.</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Shandong</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Shandong, Zibo</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>36.79</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>118.06</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>alumina</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Zouping Refinery</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Zhuhai SEZ Fangyuan Inc.</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Zhuhai SEZ Fangyuan Inc. (private, Zhuhai)</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Shandong</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Shandong, Zouping</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>36.89</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>117.77</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Unverified</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>alumina</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>HOST CONFIRMED BY ELIMINATION: Zouping county's only alumina refinery is Shandong Weiqiao (15 Mt, 1.7 km away). Fangyuan chairman lists Shandong Zouping among its 6 bases (Asian Metal 2019). Hongqiao A-share platform (002379, HQ Zouping) stated 2026-06-04 'no gallium-related production activity' — legal-entity separation, not physical absence. Current operating status unknown; Weiqiao alumina is migrating to Zhanhua.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Shanxi New Material Smelter</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Shanxi Zhaofeng Aluminum &amp; Power Co., Ltd.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Chinalco (Government)</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Shanxi</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Shanxi, Yangquan</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>35.65</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>110.66</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Assumed Active</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>alumina</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Yuanping Refinery</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Zhuhai SEZ Fangyuan Inc.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Zhuhai SEZ Fangyuan Inc. (private, Zhuhai)</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Shanxi</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Shanxi, Yuanping</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>38.79</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>112.7</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Unverified</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>alumina</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>host = SPIC Shanxi Aluminum (state power investment corp); Fangyuan chairman said in 2019 this was the base then actually operating</t>
         </is>
